--- a/results/tables/model_RAB.xlsx
+++ b/results/tables/model_RAB.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Benjamin\Oath Dropbox\Benjamin Bukombe\tea_paper\results\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD55BC3-03AA-4246-9BE4-AFCB7805F8AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1747BC2A-A6A5-46A5-AC3D-77509D83A7D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{E965CB2D-C288-4D10-BD75-EE55C6BD7B9F}"/>
+    <workbookView xWindow="71880" yWindow="1185" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E965CB2D-C288-4D10-BD75-EE55C6BD7B9F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="RAB" sheetId="1" r:id="rId1"/>
+    <sheet name="macro-scale" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
   <si>
     <t>Std.Err.</t>
   </si>
@@ -56,25 +58,91 @@
     <t>Coefficients</t>
   </si>
   <si>
-    <t>NPK70-OSL31-250</t>
-  </si>
-  <si>
-    <t>control</t>
-  </si>
-  <si>
     <t>Time</t>
   </si>
   <si>
-    <t>NPK70-OSL31-250:days_elapsed</t>
-  </si>
-  <si>
-    <t>control:days_elapsed</t>
-  </si>
-  <si>
     <t>L.CI</t>
   </si>
   <si>
-    <t>H.CI</t>
+    <t>std err</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>P&gt;|t|</t>
+  </si>
+  <si>
+    <t>coefficients</t>
+  </si>
+  <si>
+    <t>U.CI</t>
+  </si>
+  <si>
+    <t>L.CI [0.025]</t>
+  </si>
+  <si>
+    <t>U.CI [0.975]</t>
+  </si>
+  <si>
+    <t>UTC</t>
+  </si>
+  <si>
+    <t>Ntendezi</t>
+  </si>
+  <si>
+    <t>UTC:Ntendezi</t>
+  </si>
+  <si>
+    <t>UTC:Time</t>
+  </si>
+  <si>
+    <t>Ntendezi:Time</t>
+  </si>
+  <si>
+    <t>UTC:Ntendezi:Time</t>
+  </si>
+  <si>
+    <t>NPK-350kg/ha</t>
+  </si>
+  <si>
+    <t>NPK70-OSL31-250g/ha</t>
+  </si>
+  <si>
+    <t>NPK70-OSL31-250g/ha:Time</t>
+  </si>
+  <si>
+    <t>NPK-350kg/ha:Time</t>
+  </si>
+  <si>
+    <t>Treatment</t>
+  </si>
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>Bigutu (Upland-gentle slope/Baseline)</t>
+  </si>
+  <si>
+    <t>Ntendezi (Lowland-Plain)</t>
+  </si>
+  <si>
+    <t>OSL-Treated</t>
+  </si>
+  <si>
+    <t>Daily tea yield Kg day-1</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>Table X. Least Square daily cumulative tea yield across distinct topographic sites under OSL-treated and UTC.</t>
+  </si>
+  <si>
+    <t>17.29-20.94</t>
+  </si>
+  <si>
+    <t>Range</t>
   </si>
 </sst>
 </file>
@@ -115,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -123,6 +191,7 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -478,7 +547,7 @@
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>11</v>
@@ -509,7 +578,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B3" s="2">
         <v>-175.76499999999999</v>
@@ -532,7 +601,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B4" s="2">
         <v>-298.03699999999998</v>
@@ -555,7 +624,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2">
         <v>-6.7249999999999996</v>
@@ -578,7 +647,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2">
         <v>-13.153</v>
@@ -601,7 +670,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2">
         <v>30.664000000000001</v>
@@ -620,6 +689,336 @@
       </c>
       <c r="G7" s="2">
         <v>32.933999999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{740E46A4-4FDA-455D-BCB3-BACCF5DA39F2}">
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="58.59765625" customWidth="1"/>
+    <col min="2" max="2" width="15.3984375" customWidth="1"/>
+    <col min="6" max="6" width="11.265625" customWidth="1"/>
+    <col min="7" max="7" width="19.265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3">
+        <v>19.985299999999999</v>
+      </c>
+      <c r="C2" s="3">
+        <v>79.349000000000004</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0.252</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0.80200000000000005</v>
+      </c>
+      <c r="F2" s="3">
+        <v>-140.148</v>
+      </c>
+      <c r="G2" s="3">
+        <v>180.11799999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3">
+        <v>-10.3881</v>
+      </c>
+      <c r="C3" s="3">
+        <v>112.217</v>
+      </c>
+      <c r="D3" s="3">
+        <v>-9.2999999999999999E-2</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.92700000000000005</v>
+      </c>
+      <c r="F3" s="3">
+        <v>-236.85</v>
+      </c>
+      <c r="G3" s="3">
+        <v>216.07400000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="3">
+        <v>169.35</v>
+      </c>
+      <c r="C4" s="3">
+        <v>112.595</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1.504</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F4" s="3">
+        <v>-57.875999999999998</v>
+      </c>
+      <c r="G4" s="3">
+        <v>396.57600000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="3">
+        <v>-212.3331</v>
+      </c>
+      <c r="C5" s="3">
+        <v>159.23400000000001</v>
+      </c>
+      <c r="D5" s="3">
+        <v>-1.333</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.19</v>
+      </c>
+      <c r="F5" s="3">
+        <v>-533.67999999999995</v>
+      </c>
+      <c r="G5" s="3">
+        <v>109.01300000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3">
+        <v>19.113399999999999</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.90300000000000002</v>
+      </c>
+      <c r="D6" s="3">
+        <v>21.155999999999999</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>17.29</v>
+      </c>
+      <c r="G6" s="3">
+        <v>20.937000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="3">
+        <v>-7.4802999999999997</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1.278</v>
+      </c>
+      <c r="D7" s="3">
+        <v>-5.8550000000000004</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>-10.058999999999999</v>
+      </c>
+      <c r="G7" s="3">
+        <v>-4.9020000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="3">
+        <v>18.572299999999998</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1.339</v>
+      </c>
+      <c r="D8" s="3">
+        <v>13.865</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>15.869</v>
+      </c>
+      <c r="G8" s="3">
+        <v>21.274999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="3">
+        <v>-5.0651000000000002</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1.8939999999999999</v>
+      </c>
+      <c r="D9" s="3">
+        <v>-2.6739999999999999</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="F9" s="3">
+        <v>-8.8879999999999999</v>
+      </c>
+      <c r="G9" s="3">
+        <v>-1.242</v>
+      </c>
+    </row>
+    <row r="20" spans="5:7" x14ac:dyDescent="0.45">
+      <c r="E20">
+        <v>350</v>
+      </c>
+      <c r="F20">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="5:7" x14ac:dyDescent="0.45">
+      <c r="G21">
+        <f>E20*70/E22</f>
+        <v>245</v>
+      </c>
+    </row>
+    <row r="22" spans="5:7" x14ac:dyDescent="0.45">
+      <c r="E22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="5:7" x14ac:dyDescent="0.45">
+      <c r="F23">
+        <v>50</v>
+      </c>
+      <c r="G23">
+        <f>E20*F23/E22</f>
+        <v>175</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF2C441A-4A26-41BD-8CB1-8EF3C8069D11}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="32.796875" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="19.86328125" customWidth="1"/>
+    <col min="4" max="4" width="13.86328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4">
+        <v>19.11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5">
+        <v>11.63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6">
+        <v>37.68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>25.13</v>
       </c>
     </row>
   </sheetData>
